--- a/cleaned_financial_data.xlsx
+++ b/cleaned_financial_data.xlsx
@@ -1,13 +1,8 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LENOVO\Desktop\financial-data-analysis-projects\project1_python\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
   <bookViews>
     <workbookView windowWidth="23040" windowHeight="10500"/>
   </bookViews>
@@ -1471,7 +1466,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr/>
   <dimension ref="A1:BK48"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
